--- a/results/reliability_eval/Llama-3-8B_P17_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P17_sample_15_tokens_0.1_temp_deductive_reasoning_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5204210069444445</v>
+        <v>0.522242105263158</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3840185889045508</v>
+        <v>0.05428114755543099</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5204210069444445</v>
+        <v>0.522242105263158</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3840185889045508</v>
+        <v>0.05428114755543099</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4757291666666667</v>
+        <v>0.4798842105263157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3734272503238181</v>
+        <v>0.05516681178566425</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9935763888888889</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9867143941530598</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.36</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
